--- a/artfynd/A 3538-2023 artfynd.xlsx
+++ b/artfynd/A 3538-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121655533</v>
+        <v>121655531</v>
       </c>
       <c r="B2" t="n">
-        <v>79227</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608575</v>
+        <v>608560</v>
       </c>
       <c r="R2" t="n">
-        <v>6636175</v>
+        <v>6636216</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121655531</v>
+        <v>121655533</v>
       </c>
       <c r="B3" t="n">
-        <v>79725</v>
+        <v>79234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608560</v>
+        <v>608575</v>
       </c>
       <c r="R3" t="n">
-        <v>6636216</v>
+        <v>6636175</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>dm2</t>
+          <t>cm2</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3538-2023 artfynd.xlsx
+++ b/artfynd/A 3538-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121655531</v>
+        <v>121655533</v>
       </c>
       <c r="B2" t="n">
-        <v>79732</v>
+        <v>79234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608560</v>
+        <v>608575</v>
       </c>
       <c r="R2" t="n">
-        <v>6636216</v>
+        <v>6636175</v>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>dm2</t>
+          <t>cm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121655533</v>
+        <v>121655531</v>
       </c>
       <c r="B3" t="n">
-        <v>79234</v>
+        <v>79732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608575</v>
+        <v>608560</v>
       </c>
       <c r="R3" t="n">
-        <v>6636175</v>
+        <v>6636216</v>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>dm2</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3538-2023 artfynd.xlsx
+++ b/artfynd/A 3538-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121655533</v>
+        <v>121655531</v>
       </c>
       <c r="B2" t="n">
-        <v>79234</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608575</v>
+        <v>608560</v>
       </c>
       <c r="R2" t="n">
-        <v>6636175</v>
+        <v>6636216</v>
       </c>
       <c r="S2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121655531</v>
+        <v>121655533</v>
       </c>
       <c r="B3" t="n">
-        <v>79732</v>
+        <v>79234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608560</v>
+        <v>608575</v>
       </c>
       <c r="R3" t="n">
-        <v>6636216</v>
+        <v>6636175</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>dm2</t>
+          <t>cm2</t>
         </is>
       </c>
       <c r="AD3" t="b">
